--- a/Avaliações dos Itens/Pré-teste (2003 - 2007)/2003.xlsx
+++ b/Avaliações dos Itens/Pré-teste (2003 - 2007)/2003.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{4B1AC159-54ED-4621-91AF-5648AC1366B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{297D949D-A277-47CC-825A-2BAF0EF26789}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{4B1AC159-54ED-4621-91AF-5648AC1366B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7437BCDE-EBCD-495C-84F5-3E2C1BFE50AD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{9B0480E6-82AE-40B7-AF7A-8D9EADDA8F1A}"/>
+    <workbookView xWindow="30252" yWindow="783" windowWidth="22118" windowHeight="11613" xr2:uid="{9B0480E6-82AE-40B7-AF7A-8D9EADDA8F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="2003" sheetId="3" r:id="rId1"/>
@@ -191,6 +186,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -511,14 +510,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD90FD8-6163-409F-A60A-D7C5A3327D95}">
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.26953125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" style="3" customWidth="1"/>
-    <col min="3" max="5" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="39.296875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.69921875" style="3" customWidth="1"/>
+    <col min="3" max="5" width="8.69921875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
@@ -535,7 +534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,7 +568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="299" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="265" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,7 +585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="299" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="265" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -603,7 +602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -620,7 +619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -637,7 +636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -654,7 +653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -671,7 +670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="299" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="265" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -688,7 +687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="299" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="265" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -705,7 +704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="299" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="265" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -722,7 +721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="299" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="265" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,7 +755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -773,7 +772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="409.55" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -807,330 +806,331 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>